--- a/PS-VRP/dist/Schedulatore/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/dist/Schedulatore/Dati_output/schedulazione_ridotta.xlsx
@@ -38,14 +38,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
         <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -56,14 +62,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CCE5FF"/>
-        <bgColor rgb="00CCE5FF"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -568,7 +568,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>255338</v>
+        <v>254460</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>02-12-2025 08:54:23</t>
+          <t>02-12-2025 08:56:23</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>254897</v>
+        <v>254948</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 07:31:12</t>
+          <t>02-12-2025 09:43:04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 07:50:12</t>
+          <t>02-12-2025 10:00:04</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -617,12 +617,12 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>254569</v>
+        <v>255170</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 08:21:10</t>
+          <t>02-12-2025 11:19:28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:10</t>
+          <t>02-12-2025 11:53:28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>255221</v>
+        <v>254532</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -659,12 +659,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 09:17:56</t>
+          <t>02-12-2025 12:01:48</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 09:49:56</t>
+          <t>02-12-2025 12:18:48</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -673,12 +673,12 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>254739</v>
+        <v>254531</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -687,24 +687,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 10:19:57</t>
+          <t>02-12-2025 13:42:09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 10:36:57</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+          <t>02-12-2025 13:57:09</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>254736</v>
+        <v>254573</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -713,16 +715,18 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 12:09:36</t>
+          <t>02-12-2025 14:41:18</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 12:24:36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
+          <t>03-12-2025 07:13:18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -730,7 +734,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254853</v>
+        <v>254895</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -739,24 +743,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>03-12-2025 14:55:03</t>
+          <t>03-12-2025 07:59:41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 07:29:03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
+          <t>03-12-2025 08:16:41</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254856</v>
+        <v>244023</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -765,24 +771,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 08:22:03</t>
+          <t>03-12-2025 09:10:34</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 08:39:03</t>
+          <t>03-12-2025 09:33:34</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>255102</v>
+        <v>254853</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -791,12 +797,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 11:00:53</t>
+          <t>03-12-2025 09:41:53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 11:17:53</t>
+          <t>03-12-2025 09:58:53</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -808,7 +814,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>254364</v>
+        <v>254454</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -817,24 +823,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 13:40:26</t>
+          <t>03-12-2025 10:51:52</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 13:59:26</t>
+          <t>03-12-2025 11:12:52</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254898</v>
+        <v>254379</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -843,26 +849,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 14:25:55</t>
+          <t>03-12-2025 12:02:51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>04-12-2025 14:42:55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 12:25:51</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>254585</v>
+        <v>254551</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -871,12 +875,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 07:13:53</t>
+          <t>03-12-2025 13:57:27</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 07:30:53</t>
+          <t>03-12-2025 14:16:27</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -885,12 +889,12 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>254582</v>
+        <v>254915</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -899,26 +903,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 08:17:34</t>
+          <t>04-12-2025 09:26:19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 08:32:34</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>04-12-2025 09:43:19</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>254258</v>
+        <v>254819</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -927,24 +929,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 09:19:14</t>
+          <t>04-12-2025 10:32:11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 09:36:14</t>
+          <t>04-12-2025 10:53:11</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>254881</v>
+        <v>254818</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -953,156 +955,156 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 12:00:55</t>
+          <t>04-12-2025 11:47:44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>05-12-2025 12:15:55</t>
+          <t>04-12-2025 12:02:44</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>254511</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:29:00</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>254708</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>05-12-2025 14:40:35</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>05-12-2025 14:59:35</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>254894</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 09:38:35</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 10:24:35</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>255028</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>08-12-2025 08:07:26</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>08-12-2025 08:22:26</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>254424</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:12:21</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:39:21</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>254855</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:50:19</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 13:17:19</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>255233</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>08-12-2025 13:02:59</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>08-12-2025 13:17:59</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n">
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>254938</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 14:04:04</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>03-12-2025 14:31:04</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>255063</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>08-12-2025 14:50:24</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>09-12-2025 07:05:24</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>254013</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>09-12-2025 10:09:41</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>09-12-2025 10:26:41</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>254812</v>
+        <v>254978</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1111,16 +1113,18 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>04-12-2025 08:01:39</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 07:29:00</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
+          <t>04-12-2025 08:30:39</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>7</v>
@@ -1128,7 +1132,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>254573</v>
+        <v>254255</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1137,26 +1141,24 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 08:10:36</t>
+          <t>04-12-2025 08:53:28</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 08:54:36</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>04-12-2025 09:20:28</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>254895</v>
+        <v>254766</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -1165,182 +1167,186 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 09:41:00</t>
+          <t>04-12-2025 10:03:56</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>03-12-2025 10:08:00</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+          <t>04-12-2025 10:34:56</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>254872</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 07:17:00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>254645</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 11:01:53</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 11:43:53</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>254736</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 07:58:17</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 08:13:17</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>254739</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 10:43:44</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 10:58:44</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>251289</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 12:31:23</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>02-12-2025 13:03:23</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>254855</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 12:42:15</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 13:24:15</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>254819</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 14:11:00</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>03-12-2025 14:38:00</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>254818</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 07:32:33</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 07:57:33</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>254766</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 08:42:01</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 09:09:01</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>4</v>
+      <c r="A30" s="4" t="n">
+        <v>254592</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:44:25</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 08:03:25</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>254496</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 10:30:10</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>04-12-2025 10:57:10</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>7</v>
+      <c r="A31" s="4" t="n">
+        <v>254590</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 09:03:17</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 09:20:17</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>255334</v>
+        <v>254569</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
@@ -1349,16 +1355,18 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 07:00:00</t>
+          <t>03-12-2025 10:06:58</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 07:17:00</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0</v>
+          <t>03-12-2025 10:21:58</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>1</v>
@@ -1366,7 +1374,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>254872</v>
+        <v>254897</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
@@ -1375,12 +1383,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 09:50:57</t>
+          <t>03-12-2025 11:01:43</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 10:05:57</t>
+          <t>03-12-2025 11:18:43</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1394,7 +1402,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>254537</v>
+        <v>235572</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
@@ -1403,26 +1411,24 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 10:47:14</t>
+          <t>03-12-2025 11:49:41</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 11:04:14</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 12:06:41</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>254540</v>
+        <v>254359</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
@@ -1431,26 +1437,24 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 11:45:52</t>
+          <t>03-12-2025 13:29:40</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 12:00:52</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 13:44:40</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>254948</v>
+        <v>254700</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
@@ -1459,26 +1463,24 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 12:42:30</t>
+          <t>03-12-2025 14:07:52</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 13:14:30</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 14:26:52</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>254894</v>
+        <v>254645</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
@@ -1487,26 +1489,24 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 14:33:55</t>
+          <t>04-12-2025 07:58:35</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>02-12-2025 14:50:55</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>04-12-2025 08:32:35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>254590</v>
+        <v>254824</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
@@ -1515,26 +1515,24 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:41</t>
+          <t>04-12-2025 09:30:57</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 08:55:41</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>04-12-2025 09:47:57</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>235572</v>
+        <v>254535</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -1543,24 +1541,24 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 09:42:21</t>
+          <t>05-12-2025 14:16:11</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 10:01:21</t>
+          <t>05-12-2025 14:35:11</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>254359</v>
+        <v>254654</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -1569,24 +1567,24 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 11:24:20</t>
+          <t>08-12-2025 07:01:13</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 11:39:20</t>
+          <t>08-12-2025 07:37:13</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>254460</v>
+        <v>254013</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
@@ -1595,24 +1593,24 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 12:02:32</t>
+          <t>08-12-2025 08:57:44</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 12:19:32</t>
+          <t>08-12-2025 09:16:44</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>254379</v>
+        <v>254269</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
@@ -1621,24 +1619,24 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 13:06:13</t>
+          <t>08-12-2025 12:19:44</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 13:27:13</t>
+          <t>08-12-2025 12:38:44</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>254820</v>
+        <v>255084</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
@@ -1647,24 +1645,24 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>03-12-2025 14:58:49</t>
+          <t>08-12-2025 13:26:00</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025 07:19:49</t>
+          <t>08-12-2025 13:43:00</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>254454</v>
+        <v>254167</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
@@ -1673,64 +1671,66 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025 08:17:17</t>
+          <t>08-12-2025 14:30:39</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025 08:40:17</t>
+          <t>08-12-2025 14:49:39</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>254824</v>
+        <v>254866</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025 09:30:15</t>
+          <t>02-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>04-12-2025 10:12:15</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
+          <t>02-12-2025 07:32:30</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>254535</v>
+        <v>255102</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>05-12-2025 14:40:29</t>
+          <t>02-12-2025 09:33:22</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>05-12-2025 14:59:29</t>
+          <t>02-12-2025 10:07:52</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -1742,47 +1742,47 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>254657</v>
+        <v>254856</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 07:25:31</t>
+          <t>02-12-2025 12:30:25</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 07:57:31</t>
+          <t>02-12-2025 13:02:55</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>254810</v>
+        <v>254597</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 08:53:05</t>
+          <t>03-12-2025 07:24:46</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 09:12:05</t>
+          <t>03-12-2025 08:09:16</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -1794,505 +1794,505 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>254268</v>
+        <v>254598</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 11:36:45</t>
+          <t>03-12-2025 09:41:07</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 11:53:45</t>
+          <t>03-12-2025 10:11:37</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>254253</v>
+        <v>254603</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 12:45:21</t>
+          <t>03-12-2025 11:55:53</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>08-12-2025 13:02:21</t>
+          <t>03-12-2025 12:26:23</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>255338</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 13:58:14</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>03-12-2025 14:42:44</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>254866</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>254496</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>CASON</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 07:32:30</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>04-12-2025 13:19:34</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>04-12-2025 13:52:04</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>254575</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 08:05:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>254196</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 08:54:26</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 09:19:26</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 09:33:22</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:05:52</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>254424</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:14:11</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:50:41</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>254700</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 11:01:38</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 11:36:08</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>4</v>
+      <c r="F54" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>254597</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 13:07:52</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>02-12-2025 13:58:22</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
+      <c r="A55" s="2" t="n">
+        <v>254602</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 11:52:50</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 13:02:50</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>254938</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 07:30:13</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 08:20:43</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
+      <c r="A56" s="2" t="n">
+        <v>255220</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>03-12-2025 14:34:42</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>04-12-2025 07:34:42</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>254978</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 09:51:18</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 10:25:48</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>7</v>
+      <c r="A57" s="2" t="n">
+        <v>254820</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>04-12-2025 08:03:07</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>04-12-2025 08:38:07</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>254255</v>
+        <v>255334</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 10:48:37</t>
+          <t>03-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 11:21:07</t>
+          <t>03-12-2025 07:17:00</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>254196</v>
+        <v>254686</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>03-12-2025 09:50:57</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 08:05:00</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 10:07:57</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>255046</v>
+        <v>252692</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 10:38:24</t>
+          <t>03-12-2025 11:01:37</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>03-12-2025 11:08:24</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>03-12-2025 11:18:37</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
+        <v>255368</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>03-12-2025 11:53:52</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:14:52</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>255046</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
         <v>234538</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 11:56:03</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 12:21:03</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 08:22:39</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 08:47:39</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F63" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>255220</v>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 13:38:08</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 14:18:08</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="n">
-        <v>254602</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>03-12-2025 14:46:33</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>04-12-2025 07:46:33</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>255158</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 10:04:43</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 10:34:43</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="n">
-        <v>254603</v>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>04-12-2025 09:18:25</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>04-12-2025 09:43:25</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
-        <v>254598</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>04-12-2025 11:15:16</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>04-12-2025 11:40:16</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="A65" s="6" t="n">
+        <v>254812</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:00:11</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>03-12-2025 12:35:11</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>254686</v>
+        <v>254898</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>03-12-2025 13:16:48</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 07:19:00</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>0</v>
+          <t>03-12-2025 13:51:48</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>252692</v>
+        <v>254911</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 08:12:40</t>
+          <t>03-12-2025 14:22:46</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 08:29:40</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>0</v>
+          <t>03-12-2025 14:57:46</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F67" s="6" t="n">
         <v>1</v>
@@ -2300,33 +2300,33 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>255368</v>
+        <v>255027</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 09:04:54</t>
+          <t>04-12-2025 09:13:28</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 09:25:54</t>
+          <t>04-12-2025 09:38:28</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>254592</v>
+        <v>255233</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
@@ -2335,108 +2335,102 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>04-12-2025 14:23:16</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>03-12-2025 07:30:00</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>04-12-2025 14:48:16</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
-        <v>251289</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7" t="n">
+      <c r="A70" s="6" t="n">
+        <v>255028</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>05-12-2025 08:20:41</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>05-12-2025 08:45:41</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>255063</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>05-12-2025 13:26:14</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>05-12-2025 13:51:14</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>250049</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>08-12-2025 08:55:31</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>08-12-2025 09:25:31</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="6" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>255170</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:16:02</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:51:02</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="n">
-        <v>254532</v>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 10:59:22</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>02-12-2025 11:29:22</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>254511</v>
+        <v>255221</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
@@ -2445,24 +2439,26 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>02-12-2025 12:52:42</t>
+          <t>02-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>02-12-2025 13:22:42</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>0</v>
+          <t>02-12-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>255158</v>
+        <v>254540</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
@@ -2471,16 +2467,18 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 07:32:18</t>
+          <t>02-12-2025 08:05:01</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 08:07:18</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>0</v>
+          <t>02-12-2025 08:40:01</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F74" s="7" t="n">
         <v>7</v>
@@ -2488,7 +2486,7 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>254575</v>
+        <v>254537</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
@@ -2497,16 +2495,18 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 09:32:46</t>
+          <t>02-12-2025 09:21:39</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 10:12:46</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n">
-        <v>0</v>
+          <t>02-12-2025 09:46:39</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F75" s="7" t="n">
         <v>7</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>254531</v>
+        <v>254364</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
@@ -2523,26 +2523,24 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 11:02:12</t>
+          <t>02-12-2025 10:28:17</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 11:47:12</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>02-12-2025 11:03:17</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>254915</v>
+        <v>254582</v>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
@@ -2551,24 +2549,26 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 12:31:21</t>
+          <t>02-12-2025 11:29:46</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 13:11:21</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>0</v>
+          <t>02-12-2025 12:04:46</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>254911</v>
+        <v>254585</v>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:13</t>
+          <t>02-12-2025 12:51:26</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>03-12-2025 14:30:13</t>
+          <t>02-12-2025 13:16:26</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -2596,7 +2596,7 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>254551</v>
+        <v>254881</v>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
@@ -2605,26 +2605,24 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>04-12-2025 08:45:55</t>
+          <t>02-12-2025 14:03:07</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>04-12-2025 09:10:55</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>02-12-2025 14:33:07</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>255027</v>
+        <v>254258</v>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
@@ -2633,24 +2631,24 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>04-12-2025 12:20:47</t>
+          <t>03-12-2025 08:57:47</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>04-12-2025 12:45:47</t>
+          <t>03-12-2025 09:22:47</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>253862</v>
+        <v>254708</v>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
@@ -2659,16 +2657,18 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 09:30:35</t>
+          <t>03-12-2025 11:47:28</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 10:00:35</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n">
-        <v>0</v>
+          <t>03-12-2025 12:22:28</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F81" s="7" t="n">
         <v>1</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>254654</v>
+        <v>253862</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
@@ -2685,24 +2685,24 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 11:00:11</t>
+          <t>03-12-2025 13:30:19</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 11:30:11</t>
+          <t>03-12-2025 14:00:19</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>254548</v>
+        <v>254657</v>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
@@ -2711,24 +2711,24 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 12:50:42</t>
+          <t>03-12-2025 14:59:54</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 13:30:42</t>
+          <t>04-12-2025 07:34:54</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>254269</v>
+        <v>254810</v>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
@@ -2737,24 +2737,24 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 13:54:44</t>
+          <t>04-12-2025 08:30:28</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>05-12-2025 14:34:44</t>
+          <t>04-12-2025 09:05:28</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>255084</v>
+        <v>254268</v>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
@@ -2763,24 +2763,24 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 07:22:01</t>
+          <t>04-12-2025 11:30:08</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 07:52:01</t>
+          <t>04-12-2025 12:00:08</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>250049</v>
+        <v>254253</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
@@ -2789,24 +2789,24 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 08:39:40</t>
+          <t>04-12-2025 12:51:44</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 09:14:40</t>
+          <t>04-12-2025 13:21:44</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>254167</v>
+        <v>254548</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 10:58:50</t>
+          <t>05-12-2025 08:22:54</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>08-12-2025 11:33:50</t>
+          <t>05-12-2025 09:07:54</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
@@ -2885,54 +2885,54 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="2" t="n">
         <v>253902</v>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>10-12-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>10-12-2025 14:17:00</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="4" t="n">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>10-12-2025 14:19:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="4" t="n">
         <v>253408</v>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>CASON</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>09-12-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>09-12-2025 14:36:30</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="5" t="n">
+      <c r="E91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
         <v>4</v>
       </c>
     </row>
